--- a/data/trans_orig/P20B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P20B-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2007</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2007 (tasa de respuesta: 99,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5602</t>
+          <t>5587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,44%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6731</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>30,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4476</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>9234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,73%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10611</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12585</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15932</t>
+          <t>15730</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>21850</t>
+          <t>21853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>9564</t>
+          <t>10427</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,05%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4114</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15780</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,38%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8090</t>
+          <t>8201</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21432</t>
+          <t>21522</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>15389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,95%</t>
+          <t>59,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>31495</t>
+          <t>32744</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>42514</t>
+          <t>43161</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,62%</t>
+          <t>69,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>91,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51659</t>
+          <t>51569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>65001</t>
+          <t>64890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4825</t>
+          <t>3917</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>53,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>6151</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>887</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7390</t>
+          <t>7748</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2550</t>
+          <t>3458</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>46,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10368</t>
+          <t>10173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>16309</t>
+          <t>15951</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22809</t>
+          <t>22812</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>67,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>3454</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>11798</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,87%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>3565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12364</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3263</t>
+          <t>3438</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8025</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15901</t>
+          <t>15154</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,13%</t>
+          <t>36,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,45%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13638</t>
+          <t>13241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22362</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>50,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6327</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5441</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,88%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8242</t>
+          <t>8615</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6843</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12231</t>
+          <t>12272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>14552</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>71,12%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23653</t>
+          <t>23280</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>30990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>74,16%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>97,16%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>898</t>
+          <t>869</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>6550</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2606</t>
+          <t>2126</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5448</t>
+          <t>4882</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16056</t>
+          <t>15875</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,68%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>3916</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9568</t>
+          <t>9597</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>19447</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>27966</t>
+          <t>28446</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>93,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24982</t>
+          <t>25163</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35590</t>
+          <t>36156</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>7456</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18662</t>
+          <t>18525</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,75%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9868</t>
+          <t>10413</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23492</t>
+          <t>23087</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>19,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20912</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37705</t>
+          <t>37909</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,2%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15426</t>
+          <t>15563</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26795</t>
+          <t>26632</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,61%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30176</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43800</t>
+          <t>43255</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,61%</t>
+          <t>80,6%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>50051</t>
+          <t>49847</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>67340</t>
+          <t>66844</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,73%</t>
+          <t>76,17%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2931</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11610</t>
+          <t>11560</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4780</t>
+          <t>4847</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>16227</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9997</t>
+          <t>10776</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23632</t>
+          <t>24244</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,81%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>14151</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22780</t>
+          <t>22942</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34382</t>
+          <t>34267</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45714</t>
+          <t>45647</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,4%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>52573</t>
+          <t>51961</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>66208</t>
+          <t>65429</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25274</t>
+          <t>26122</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45688</t>
+          <t>45854</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>34,22%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>38941</t>
+          <t>36755</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62932</t>
+          <t>62079</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>69951</t>
+          <t>71546</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>102057</t>
+          <t>102438</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>18,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,69%</t>
+          <t>26,79%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>88294</t>
+          <t>88128</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>108708</t>
+          <t>107860</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>65,78%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>185435</t>
+          <t>186288</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>209426</t>
+          <t>211612</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>280292</t>
+          <t>279911</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>312398</t>
+          <t>310803</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,31%</t>
+          <t>73,21%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,7%</t>
+          <t>81,29%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2012</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2012 (tasa de respuesta: 99,21%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7486</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17629</t>
+          <t>17626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5275</t>
+          <t>5671</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16394</t>
+          <t>16901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,39%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15843</t>
+          <t>15408</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>31260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,79%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6875</t>
+          <t>6878</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17018</t>
+          <t>17435</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,45%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20538</t>
+          <t>20031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31657</t>
+          <t>31261</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,61%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>29573</t>
+          <t>30177</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>45594</t>
+          <t>46029</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>74,92%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6271</t>
+          <t>5290</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19129</t>
+          <t>18950</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8580</t>
+          <t>8447</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22642</t>
+          <t>22693</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>17533</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36753</t>
+          <t>36505</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>35,87%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23087</t>
+          <t>23266</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>35945</t>
+          <t>36926</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>54,69%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36917</t>
+          <t>36866</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>50979</t>
+          <t>51112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>61,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65022</t>
+          <t>65270</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84517</t>
+          <t>84242</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>82,77%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9816</t>
+          <t>10497</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4903</t>
+          <t>4953</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15549</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>8019</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21472</t>
+          <t>20637</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>35,33%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14628</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>22407</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>91,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18400</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29065</t>
+          <t>29015</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>36941</t>
+          <t>37776</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50232</t>
+          <t>50394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>85,99%</t>
+          <t>86,27%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1808</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9556</t>
+          <t>9506</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3288</t>
+          <t>3219</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>13427</t>
+          <t>14062</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7142</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>20282</t>
+          <t>19164</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>33,83%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10596</t>
+          <t>10646</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18332</t>
+          <t>18344</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>22428</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33202</t>
+          <t>33271</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>61,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>36359</t>
+          <t>37477</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49499</t>
+          <t>49899</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,19%</t>
+          <t>66,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>88,1%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3241</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10388</t>
+          <t>10339</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2097</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>10956</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7168</t>
+          <t>7928</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18861</t>
+          <t>18578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>54,5%</t>
+          <t>53,69%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2828</t>
+          <t>2877</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9975</t>
+          <t>10225</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9406</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19293</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>15745</t>
+          <t>16028</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27438</t>
+          <t>26678</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,29%</t>
+          <t>77,09%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1129</t>
+          <t>1135</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9687</t>
+          <t>9995</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>64,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1037</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>9605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>35,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4378</t>
+          <t>4277</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17614</t>
+          <t>16950</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>40,22%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5698</t>
+          <t>5390</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14256</t>
+          <t>14250</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,03%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25723</t>
+          <t>25719</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,75%</t>
+          <t>64,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,14%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24527</t>
+          <t>25191</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37763</t>
+          <t>37864</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,85%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4644</t>
+          <t>4724</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>15620</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>52,97%</t>
+          <t>50,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22249</t>
+          <t>23093</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>16729</t>
+          <t>17410</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>34355</t>
+          <t>33666</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,42%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>14460</t>
+          <t>15129</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26105</t>
+          <t>26025</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,03%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,9%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>36423</t>
+          <t>35579</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50058</t>
+          <t>49373</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>60,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,32%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55066</t>
+          <t>55755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72692</t>
+          <t>72011</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>61,58%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>80,53%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2230</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11836</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8934</t>
+          <t>9102</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23755</t>
+          <t>23642</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14671</t>
+          <t>13694</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31643</t>
+          <t>31286</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>31,97%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25263</t>
+          <t>25368</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34869</t>
+          <t>35081</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>37127</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51835</t>
+          <t>51667</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>66224</t>
+          <t>66581</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>83196</t>
+          <t>84173</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,01%</t>
+          <t>86,01%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>48081</t>
+          <t>49306</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>78523</t>
+          <t>78396</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,79%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>66124</t>
+          <t>66734</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>98443</t>
+          <t>98841</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,77%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>125411</t>
+          <t>122540</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>166042</t>
+          <t>167472</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>30,88%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>129242</t>
+          <t>129369</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>159684</t>
+          <t>158459</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>62,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>236093</t>
+          <t>235695</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>268412</t>
+          <t>267802</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,23%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>376259</t>
+          <t>374829</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>416890</t>
+          <t>419761</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,38%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,87%</t>
+          <t>77,4%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2016</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2016 (tasa de respuesta: 98,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2036</t>
+          <t>2084</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9627</t>
+          <t>9617</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2548</t>
+          <t>2598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10774</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6158</t>
+          <t>6229</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>17937</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,42%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6014</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13605</t>
+          <t>13557</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22839</t>
+          <t>22113</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31065</t>
+          <t>31015</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>65,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31105</t>
+          <t>31317</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43096</t>
+          <t>43025</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,35%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11321</t>
+          <t>11511</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3735</t>
+          <t>3706</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15586</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9257</t>
+          <t>8620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24941</t>
+          <t>23010</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>40,33%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9670</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17858</t>
+          <t>18583</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20481</t>
+          <t>20963</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>32361</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,79%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32118</t>
+          <t>34049</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47802</t>
+          <t>48439</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>59,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,78%</t>
+          <t>84,89%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>766</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5419</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3025</t>
+          <t>3204</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12676</t>
+          <t>12871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4729</t>
+          <t>4992</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15492</t>
+          <t>16057</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>38,65%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3666</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,24%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19799</t>
+          <t>19604</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29450</t>
+          <t>29271</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26051</t>
+          <t>25486</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36814</t>
+          <t>36551</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,71%</t>
+          <t>61,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>87,98%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4156</t>
+          <t>3954</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13939</t>
+          <t>13799</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6002</t>
+          <t>5551</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18138</t>
+          <t>17809</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12816</t>
+          <t>12269</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28731</t>
+          <t>27720</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>46,24%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14118</t>
+          <t>14258</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>23901</t>
+          <t>24103</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,19%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>13752</t>
+          <t>14081</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25888</t>
+          <t>26339</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>44,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>31216</t>
+          <t>32227</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47131</t>
+          <t>47678</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>53,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7669</t>
+          <t>7611</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,49%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>906</t>
+          <t>963</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7636</t>
+          <t>7487</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,93%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4272</t>
+          <t>4437</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13187</t>
+          <t>13199</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,24%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>1056</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6760</t>
+          <t>6764</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>78,04%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3605</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,07%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6721</t>
+          <t>6709</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15636</t>
+          <t>15471</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>77,71%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2755</t>
+          <t>2657</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11398</t>
+          <t>10813</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,69%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3414</t>
+          <t>3931</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13673</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9087</t>
+          <t>8259</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22058</t>
+          <t>21812</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>48,79%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6784</t>
+          <t>7369</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15427</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,31%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12847</t>
+          <t>12642</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23106</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>85,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22645</t>
+          <t>22891</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35616</t>
+          <t>36444</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>51,21%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>81,53%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15393</t>
+          <t>15430</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6311</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>18890</t>
+          <t>19176</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>13535</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29979</t>
+          <t>29514</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>39,7%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>10730</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21912</t>
+          <t>21945</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29300</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41879</t>
+          <t>41400</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44371</t>
+          <t>44836</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>61156</t>
+          <t>60815</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>60,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>81,8%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>17865</t>
+          <t>18035</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4423</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16089</t>
+          <t>15996</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>32,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13590</t>
+          <t>13231</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>29645</t>
+          <t>30969</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>15,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17846</t>
+          <t>17676</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>28981</t>
+          <t>29239</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,97%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33444</t>
+          <t>33537</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45110</t>
+          <t>44988</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>91,07%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>55599</t>
+          <t>54275</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>71654</t>
+          <t>72013</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>84,48%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>42502</t>
+          <t>41819</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>66360</t>
+          <t>67203</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>51703</t>
+          <t>50800</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>79847</t>
+          <t>81415</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>18,85%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>101246</t>
+          <t>102423</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>140920</t>
+          <t>142450</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,97%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>96117</t>
+          <t>95274</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>119975</t>
+          <t>120658</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>189684</t>
+          <t>188116</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>217828</t>
+          <t>218731</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,82%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>291088</t>
+          <t>289558</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>330762</t>
+          <t>329585</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,56%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2023</t>
+          <t>Población según si estuvo en lista de espera por ingreso hospitalario en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>5997</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>1063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2299</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9862</t>
+          <t>9592</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>31,0%</t>
         </is>
       </c>
     </row>
@@ -10815,7 +10815,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -10830,7 +10830,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13733</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17828</t>
+          <t>17831</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21076</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28639</t>
+          <t>28826</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8619</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22097</t>
+          <t>21724</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2977</t>
+          <t>3162</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10615</t>
+          <t>10502</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>13215</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29577</t>
+          <t>29148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>21,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>47,66%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>17020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30125</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11796</t>
+          <t>11909</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19434</t>
+          <t>19249</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>53,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,72%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31578</t>
+          <t>32007</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46544</t>
+          <t>47940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>78,39%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6520</t>
+          <t>6971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15317</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,43%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3989</t>
+          <t>3773</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11366</t>
+          <t>11101</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,61%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12732</t>
+          <t>12278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24813</t>
+          <t>24363</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,61%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11824</t>
+          <t>11015</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20621</t>
+          <t>20170</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>74,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21478</t>
+          <t>21743</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28855</t>
+          <t>29071</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35172</t>
+          <t>35622</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47253</t>
+          <t>47707</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>59,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>79,53%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3988</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14070</t>
+          <t>13587</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>60,55%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>5191</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17656</t>
+          <t>19015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11676</t>
+          <t>11479</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27522</t>
+          <t>27929</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,39%</t>
+          <t>49,11%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9167</t>
+          <t>9650</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>19417</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28593</t>
+          <t>28447</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29353</t>
+          <t>28946</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45199</t>
+          <t>45396</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>79,82%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>623</t>
+          <t>654</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3813</t>
+          <t>3806</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,5%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>344</t>
+          <t>335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2812</t>
+          <t>2782</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1600</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5809</t>
+          <t>6057</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>48,21%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>493</t>
+          <t>507</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3683</t>
+          <t>3655</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,5%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5445</t>
+          <t>5475</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7913</t>
+          <t>7922</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6756</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>11156</t>
+          <t>10965</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>53,77%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3654</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>9774</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1209</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6710</t>
+          <t>6459</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5846</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13981</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>29,86%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14336</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20687</t>
+          <t>20598</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14867</t>
+          <t>15118</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>20535</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31849</t>
+          <t>32147</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39984</t>
+          <t>39992</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>70,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,26%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14958</t>
+          <t>14900</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10172</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20626</t>
+          <t>20605</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17618</t>
+          <t>17571</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>32159</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20284</t>
+          <t>20342</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>30196</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30209</t>
+          <t>30230</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40663</t>
+          <t>40116</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>78,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>53918</t>
+          <t>54426</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>68459</t>
+          <t>68506</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,59%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3720</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,17%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1822</t>
+          <t>1768</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7861</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>7871</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>18804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>36,53%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11383</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19370</t>
+          <t>19214</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20526</t>
+          <t>20337</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26565</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33971</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44277</t>
+          <t>43606</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>84,71%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>50441</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>74594</t>
+          <t>74818</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>39667</t>
+          <t>40092</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>60527</t>
+          <t>61718</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>95101</t>
+          <t>96172</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>129204</t>
+          <t>129947</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,09%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113464</t>
+          <t>113240</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>138419</t>
+          <t>137617</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,33%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>156316</t>
+          <t>155125</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>177176</t>
+          <t>176751</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,09%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,71%</t>
+          <t>81,51%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>275698</t>
+          <t>274955</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>309801</t>
+          <t>308730</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20B-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P20B-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>844</t>
+          <t>833</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5587</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -808,7 +808,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6933</t>
+          <t>6923</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,59%</t>
+          <t>30,55%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4491</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9234</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>15730</t>
+          <t>15740</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,41%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>1851</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10427</t>
+          <t>9998</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4826</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>14934</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8201</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21522</t>
+          <t>22248</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>30,44%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15389</t>
+          <t>15818</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23944</t>
+          <t>23965</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>32744</t>
+          <t>32341</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>43161</t>
+          <t>42449</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>89,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>51569</t>
+          <t>50843</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64890</t>
+          <t>64645</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6151</t>
+          <t>6667</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>895</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7748</t>
+          <t>7026</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>29,65%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>10173</t>
+          <t>9657</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,32%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15951</t>
+          <t>16673</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22812</t>
+          <t>22804</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>70,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,26%</t>
+          <t>96,22%</t>
         </is>
       </c>
     </row>
@@ -1767,7 +1767,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3957</t>
+          <t>3893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11798</t>
+          <t>10656</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18,56%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>63,4%</t>
+          <t>57,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3565</t>
+          <t>3610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12761</t>
+          <t>12309</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,08%</t>
+          <t>47,34%</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1875,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3438</t>
+          <t>3502</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>47,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>7952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15154</t>
+          <t>15730</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>36,6%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>84,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13241</t>
+          <t>13693</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22437</t>
+          <t>22392</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,92%</t>
+          <t>52,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>781</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6327</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>4290</t>
+          <t>4269</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>905</t>
+          <t>935</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8615</t>
+          <t>9496</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>29,77%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12272</t>
+          <t>13053</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14552</t>
+          <t>14573</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23280</t>
+          <t>22399</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30990</t>
+          <t>30960</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>869</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>7367</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2126</t>
+          <t>2674</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11125</t>
+          <t>11163</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15875</t>
+          <t>15561</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>37,92%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3916</t>
+          <t>3099</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19447</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>28446</t>
+          <t>27898</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>63,61%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25163</t>
+          <t>25477</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36156</t>
+          <t>36078</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>87,91%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7456</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18525</t>
+          <t>18239</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10413</t>
+          <t>10015</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23087</t>
+          <t>23052</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,95%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20912</t>
+          <t>20932</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>37909</t>
+          <t>38949</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>44,38%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15563</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26632</t>
+          <t>27203</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>78,13%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30581</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>43255</t>
+          <t>43653</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>57,05%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>49847</t>
+          <t>48807</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>66844</t>
+          <t>66824</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,15%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>3115</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11560</t>
+          <t>11574</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>45,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4780</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>15581</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10776</t>
+          <t>9938</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>24244</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14151</t>
+          <t>14137</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>22942</t>
+          <t>22596</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>54,98%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>87,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34267</t>
+          <t>34913</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>45647</t>
+          <t>45714</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>51961</t>
+          <t>52692</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>65429</t>
+          <t>66267</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>69,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,96%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>26122</t>
+          <t>26457</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45854</t>
+          <t>45426</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>33,9%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>36755</t>
+          <t>38624</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>62079</t>
+          <t>63528</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,55%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>71546</t>
+          <t>70362</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>102438</t>
+          <t>102503</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,71%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>26,81%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>88128</t>
+          <t>88556</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>107860</t>
+          <t>107525</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>186288</t>
+          <t>184839</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>211612</t>
+          <t>209743</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>75,0%</t>
+          <t>74,42%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>279911</t>
+          <t>279846</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>310803</t>
+          <t>311987</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>81,29%</t>
+          <t>81,6%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>7549</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17626</t>
+          <t>17703</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5671</t>
+          <t>6019</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16901</t>
+          <t>17252</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>15408</t>
+          <t>15347</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>31260</t>
+          <t>30574</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>49,77%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6878</t>
+          <t>6801</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17435</t>
+          <t>16955</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,15%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20031</t>
+          <t>19680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31261</t>
+          <t>30913</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>83,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>30177</t>
+          <t>30863</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>46029</t>
+          <t>46090</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>75,02%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5290</t>
+          <t>5804</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18950</t>
+          <t>18640</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8447</t>
+          <t>8540</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22693</t>
+          <t>22461</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,1%</t>
+          <t>37,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>17533</t>
+          <t>17632</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>36505</t>
+          <t>35521</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>34,9%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>23266</t>
+          <t>23576</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36926</t>
+          <t>36412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,47%</t>
+          <t>86,25%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>36866</t>
+          <t>37098</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51112</t>
+          <t>51019</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,9%</t>
+          <t>62,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,82%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>65270</t>
+          <t>66254</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>84242</t>
+          <t>84143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>65,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>82,68%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10497</t>
+          <t>10349</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>42,94%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4953</t>
+          <t>4986</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15549</t>
+          <t>15328</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,78%</t>
+          <t>45,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8019</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20637</t>
+          <t>21835</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>37,38%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13947</t>
+          <t>14095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22407</t>
+          <t>22553</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,67%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18419</t>
+          <t>18640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29015</t>
+          <t>28982</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>85,42%</t>
+          <t>85,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>37776</t>
+          <t>36578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>50394</t>
+          <t>49560</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>84,84%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1808</t>
+          <t>1811</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>9045</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3219</t>
+          <t>3319</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>13510</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>37,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>6565</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19164</t>
+          <t>18751</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,11%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>10646</t>
+          <t>11107</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18344</t>
+          <t>18341</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>52,83%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>22428</t>
+          <t>22980</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>33271</t>
+          <t>33171</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,46%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37477</t>
+          <t>37890</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49899</t>
+          <t>50076</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,1%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10339</t>
+          <t>10923</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>29,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,23%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10956</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7928</t>
+          <t>7835</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18578</t>
+          <t>19421</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,69%</t>
+          <t>56,12%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2877</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10225</t>
+          <t>9374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>17,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>70,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10434</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19306</t>
+          <t>19311</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>45,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,26%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16028</t>
+          <t>15185</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>26678</t>
+          <t>26771</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,31%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,36%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1135</t>
+          <t>1383</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9995</t>
+          <t>9582</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1037</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>9605</t>
+          <t>9352</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>4236</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>16315</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>38,71%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5390</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>14250</t>
+          <t>14002</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25719</t>
+          <t>25682</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,1%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25191</t>
+          <t>25826</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>37864</t>
+          <t>37905</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>89,95%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4724</t>
+          <t>5073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>15,36%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>8514</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23093</t>
+          <t>23513</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17410</t>
+          <t>16420</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>33666</t>
+          <t>34030</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>38,06%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>15129</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>26025</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>35579</t>
+          <t>35159</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49373</t>
+          <t>50158</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,64%</t>
+          <t>59,93%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>55755</t>
+          <t>55391</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>72011</t>
+          <t>73001</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>61,94%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>81,64%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2314</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11731</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>9102</t>
+          <t>9017</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23642</t>
+          <t>24429</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13694</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31286</t>
+          <t>31048</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,72%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>25368</t>
+          <t>24976</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>35081</t>
+          <t>34785</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>37127</t>
+          <t>36340</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>51667</t>
+          <t>51752</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>59,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>85,02%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>66581</t>
+          <t>66819</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>84173</t>
+          <t>83746</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,57%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49306</t>
+          <t>48660</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>78396</t>
+          <t>77457</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>66734</t>
+          <t>67275</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>98841</t>
+          <t>99595</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>29,55%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>122540</t>
+          <t>125932</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>167472</t>
+          <t>166310</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,88%</t>
+          <t>30,67%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>129369</t>
+          <t>130308</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>158459</t>
+          <t>159105</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>235695</t>
+          <t>234941</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>267802</t>
+          <t>267261</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>70,45%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>79,89%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>374829</t>
+          <t>375991</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>419761</t>
+          <t>416369</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,12%</t>
+          <t>69,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>76,78%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2084</t>
+          <t>1987</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9617</t>
+          <t>9461</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2598</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>10535</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,21%</t>
+          <t>31,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6229</t>
+          <t>6084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17937</t>
+          <t>17986</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,52%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6024</t>
+          <t>6180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22113</t>
+          <t>23078</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>31015</t>
+          <t>31710</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,79%</t>
+          <t>68,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>92,27%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>31317</t>
+          <t>31268</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>43025</t>
+          <t>43170</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,65%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2365</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11511</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,84%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3706</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>15896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8620</t>
+          <t>9754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23010</t>
+          <t>23804</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>41,72%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>9135</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18583</t>
+          <t>18626</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>45,16%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>20963</t>
+          <t>20171</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>32361</t>
+          <t>32085</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>34049</t>
+          <t>33255</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>48439</t>
+          <t>47305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,67%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,89%</t>
+          <t>82,91%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>766</t>
+          <t>781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5484</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>3175</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12871</t>
+          <t>12634</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4992</t>
+          <t>4996</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16057</t>
+          <t>15722</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>37,85%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3666</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8286</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>39,51%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,55%</t>
+          <t>91,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>19604</t>
+          <t>19841</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29271</t>
+          <t>29300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,13%</t>
+          <t>90,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25486</t>
+          <t>25821</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>36551</t>
+          <t>36547</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>87,97%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3954</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13799</t>
+          <t>14144</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5726</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17809</t>
+          <t>17652</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>11627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27720</t>
+          <t>27457</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>19,39%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>45,8%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14258</t>
+          <t>13913</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24103</t>
+          <t>24043</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>49,59%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t>14238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26339</t>
+          <t>26164</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,16%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>32227</t>
+          <t>32490</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47678</t>
+          <t>48320</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>80,61%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1903</t>
+          <t>1779</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7611</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>924</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7487</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13199</t>
+          <t>13115</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>65,88%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6764</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>79,47%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3754</t>
+          <t>3742</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6709</t>
+          <t>6793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15471</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>33,7%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>77,71%</t>
+          <t>76,67%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2657</t>
+          <t>2612</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10813</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3931</t>
+          <t>3593</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>14055</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>53,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8259</t>
+          <t>8893</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21812</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,79%</t>
+          <t>48,81%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>7369</t>
+          <t>7291</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15525</t>
+          <t>15570</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12642</t>
+          <t>12465</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22589</t>
+          <t>22927</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>85,18%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>22891</t>
+          <t>22884</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36444</t>
+          <t>35810</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,53%</t>
+          <t>80,11%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>3587</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15430</t>
+          <t>14704</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>56,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>6416</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>19176</t>
+          <t>19340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>39,79%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>13535</t>
+          <t>13129</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>29514</t>
+          <t>29452</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>39,61%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>10730</t>
+          <t>11456</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21945</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>43,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,89%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>29014</t>
+          <t>28850</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41400</t>
+          <t>41774</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>59,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>44836</t>
+          <t>44898</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>60815</t>
+          <t>61221</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,39%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,34%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6472</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>18035</t>
+          <t>17557</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>4517</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15996</t>
+          <t>15941</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>13624</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30969</t>
+          <t>29565</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>34,68%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17676</t>
+          <t>18154</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>29518</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33537</t>
+          <t>33592</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>44988</t>
+          <t>45016</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>54275</t>
+          <t>55679</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>72013</t>
+          <t>71620</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>65,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,02%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>41819</t>
+          <t>43294</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>67203</t>
+          <t>68491</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>50800</t>
+          <t>52809</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>81415</t>
+          <t>81571</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>102423</t>
+          <t>101805</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>142450</t>
+          <t>140282</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>95274</t>
+          <t>93986</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>120658</t>
+          <t>119183</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>188116</t>
+          <t>187960</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>218731</t>
+          <t>216722</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>69,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,15%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>289558</t>
+          <t>291726</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>329585</t>
+          <t>330203</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -10697,7 +10697,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2471</t>
+          <t>2141</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -10707,12 +10707,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5997</t>
+          <t>5768</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -10722,7 +10722,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2992</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>5860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5154</t>
+          <t>5134</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>2465</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9592</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -10810,27 +10810,27 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9573</t>
+          <t>9532</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>5905</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16211</t>
+          <t>19217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>16349</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17831</t>
+          <t>21122</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>85,8%</t>
+          <t>86,53%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>25784</t>
+          <t>28748</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21346</t>
+          <t>23979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28826</t>
+          <t>31417</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,34%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,73%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12044</t>
+          <t>11673</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18894</t>
+          <t>22209</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>30938</t>
+          <t>33882</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15203</t>
+          <t>16718</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>10802</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21724</t>
+          <t>24193</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6090</t>
+          <t>6554</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3162</t>
+          <t>3434</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10502</t>
+          <t>10869</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21293</t>
+          <t>23272</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29148</t>
+          <t>31481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>23,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,66%</t>
+          <t>48,18%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>23541</t>
+          <t>24222</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>30071</t>
+          <t>30138</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,93%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>16321</t>
+          <t>17842</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11909</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>19249</t>
+          <t>20962</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>72,82%</t>
+          <t>73,13%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,14%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>39862</t>
+          <t>42063</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32007</t>
+          <t>33854</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>47940</t>
+          <t>50202</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,34%</t>
+          <t>51,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>76,84%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38744</t>
+          <t>40940</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>22411</t>
+          <t>24396</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>61155</t>
+          <t>65335</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>61155</t>
+          <t>65335</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>61155</t>
+          <t>65335</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10706</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6971</t>
+          <t>6442</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16126</t>
+          <t>15072</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>40,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6813</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3864</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11101</t>
+          <t>11004</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>17876</t>
+          <t>17663</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12278</t>
+          <t>12391</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24363</t>
+          <t>23355</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,51%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>40,61%</t>
+          <t>39,02%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16079</t>
+          <t>15888</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11015</t>
+          <t>11522</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>20170</t>
+          <t>20152</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>75,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>26031</t>
+          <t>26306</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>21743</t>
+          <t>22259</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>29071</t>
+          <t>29399</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>42109</t>
+          <t>42194</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47707</t>
+          <t>47466</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,49%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>59,39%</t>
+          <t>60,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,53%</t>
+          <t>79,3%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27141</t>
+          <t>26594</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>33263</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>33263</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>32844</t>
+          <t>33263</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>59985</t>
+          <t>59857</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>59985</t>
+          <t>59857</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>59985</t>
+          <t>59857</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>8663</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3820</t>
+          <t>5550</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13587</t>
+          <t>17423</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>37,28%</t>
+          <t>38,89%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>11463</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5191</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>19015</t>
+          <t>20550</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,53%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>19004</t>
+          <t>22217</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11479</t>
+          <t>13875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>27929</t>
+          <t>32913</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>33,41%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,97%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14574</t>
+          <t>16900</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>10231</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>19417</t>
+          <t>22104</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,72%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23298</t>
+          <t>26748</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>14623</t>
+          <t>17661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>28447</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>69,26%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>46,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>37871</t>
+          <t>43648</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28946</t>
+          <t>32952</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45396</t>
+          <t>51990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>66,59%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>78,93%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>27654</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>27654</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23237</t>
+          <t>27654</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33638</t>
+          <t>38211</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>56875</t>
+          <t>65865</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56875</t>
+          <t>65865</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>56875</t>
+          <t>65865</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2283</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>679</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>3806</t>
+          <t>4022</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1195</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>335</t>
+          <t>376</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2782</t>
+          <t>3007</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3643</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6057</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>47,23%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2085</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>510</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>85,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>7127</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5475</t>
+          <t>5973</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7922</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>9152</t>
+          <t>9870</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6508</t>
+          <t>7131</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>10965</t>
+          <t>11885</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,79%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,95%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4308</t>
+          <t>4533</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>8980</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12565</t>
+          <t>13513</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>6220</t>
+          <t>6103</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3654</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>9834</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>3284</t>
+          <t>3313</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>6870</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>9504</t>
+          <t>9416</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>5838</t>
+          <t>5695</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>13683</t>
+          <t>14396</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>20,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,92%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>18032</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>14427</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>20598</t>
+          <t>21144</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>59,7%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>18293</t>
+          <t>18989</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>15118</t>
+          <t>15432</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>20535</t>
+          <t>21078</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>36326</t>
+          <t>37147</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32147</t>
+          <t>32167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>39992</t>
+          <t>40868</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,77%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>24252</t>
+          <t>24261</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21577</t>
+          <t>22302</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>45830</t>
+          <t>46563</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45830</t>
+          <t>46563</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>45830</t>
+          <t>46563</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>10690</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5046</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14900</t>
+          <t>17709</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>42,28%</t>
+          <t>40,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>15181</t>
+          <t>19976</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>13767</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20605</t>
+          <t>27287</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>24154</t>
+          <t>30666</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17571</t>
+          <t>22588</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>31651</t>
+          <t>40097</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>26268</t>
+          <t>32732</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>20342</t>
+          <t>25713</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30196</t>
+          <t>37795</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>57,72%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35654</t>
+          <t>43837</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>30230</t>
+          <t>36526</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>40116</t>
+          <t>50046</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>70,14%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>57,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,91%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>61923</t>
+          <t>76569</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>54426</t>
+          <t>67138</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>68506</t>
+          <t>84647</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>78,94%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>35242</t>
+          <t>43422</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>50835</t>
+          <t>63813</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>50835</t>
+          <t>63813</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50835</t>
+          <t>63813</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>86077</t>
+          <t>107235</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>86077</t>
+          <t>107235</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>86077</t>
+          <t>107235</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>7400</t>
+          <t>8643</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>13470</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>51,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1768</t>
+          <t>1975</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>8770</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>28,36%</t>
+          <t>27,16%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>11722</t>
+          <t>13477</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7871</t>
+          <t>8806</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18804</t>
+          <t>19934</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>36,53%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>15690</t>
+          <t>17458</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11383</t>
+          <t>12631</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>19214</t>
+          <t>21205</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>66,89%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>48,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>24065</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>20337</t>
+          <t>23524</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>30319</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>71,64%</t>
+          <t>72,84%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>39755</t>
+          <t>44918</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32673</t>
+          <t>38461</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>43606</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,92%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>23090</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>23090</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>23090</t>
+          <t>26101</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>28387</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>28387</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28387</t>
+          <t>32294</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>58395</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>58395</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>51477</t>
+          <t>58395</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>62276</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>50441</t>
+          <t>54867</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>74818</t>
+          <t>81090</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>57285</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40092</t>
+          <t>45331</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>61718</t>
+          <t>71653</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>29,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>112120</t>
+          <t>125487</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>96172</t>
+          <t>108858</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>129947</t>
+          <t>144554</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>32,09%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>125782</t>
+          <t>136976</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>113240</t>
+          <t>124088</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>137617</t>
+          <t>150311</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>60,22%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>167000</t>
+          <t>188182</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>155125</t>
+          <t>173814</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>176751</t>
+          <t>200136</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>76,66%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>292782</t>
+          <t>325158</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>274955</t>
+          <t>306091</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>308730</t>
+          <t>341787</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,15%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,84%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>188058</t>
+          <t>205178</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>216843</t>
+          <t>245467</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>404902</t>
+          <t>450645</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
